--- a/backend-erp/database/seeders/data/produits_finis_classifies.xlsx
+++ b/backend-erp/database/seeders/data/produits_finis_classifies.xlsx
@@ -1,30 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProjetErp\ERP-CMP\backend-erp\database\seeders\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDAB932-FBB2-4125-A67F-F654E1033FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305"/>
   </bookViews>
   <sheets>
     <sheet name="Produits_classifies" sheetId="1" r:id="rId1"/>
-    <sheet name="Reference_categories" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produits_classifies!$A$1:$J$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produits_classifies!$A$1:$J$83</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="202">
   <si>
     <t>Nomencla</t>
   </si>
@@ -578,27 +571,6 @@
     <t>1L Carré Strié</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Nom complet</t>
-  </si>
-  <si>
-    <t>Bouteilles PET (soufflage)</t>
-  </si>
-  <si>
-    <t>Produits HDPE (injection/extrusion-soufflage)</t>
-  </si>
-  <si>
-    <t>Injection (mug, seau, cuvette, ardoise...)</t>
-  </si>
-  <si>
-    <t>MCH</t>
-  </si>
-  <si>
-    <t>Autre / mélange (non utilisé dans ce lot)</t>
-  </si>
-  <si>
     <t xml:space="preserve">CAPS </t>
   </si>
   <si>
@@ -621,13 +593,43 @@
   </si>
   <si>
     <t>Categorie-id</t>
+  </si>
+  <si>
+    <t>Huilerie 1L</t>
+  </si>
+  <si>
+    <t>Bassine coulleur assorti</t>
+  </si>
+  <si>
+    <t>Huilerie 250 ML</t>
+  </si>
+  <si>
+    <t>Huilerie 500 ML</t>
+  </si>
+  <si>
+    <t>1L</t>
+  </si>
+  <si>
+    <t>PF-PET-032</t>
+  </si>
+  <si>
+    <t>PF-PET-033</t>
+  </si>
+  <si>
+    <t>PF-PET-034</t>
+  </si>
+  <si>
+    <t>PF-INJ-034</t>
+  </si>
+  <si>
+    <t>Seau Vert C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -643,10 +645,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -668,7 +666,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -691,6 +689,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C6D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7C6D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -706,8 +715,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1009,9 +1022,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K82"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K86"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -1025,15 +1038,15 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -1042,22 +1055,22 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1074,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G2">
         <v>300</v>
@@ -1090,7 +1103,7 @@
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1107,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G3">
         <v>300</v>
@@ -1123,7 +1136,7 @@
       </c>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1140,7 +1153,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G4">
         <v>300</v>
@@ -1156,7 +1169,7 @@
       </c>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -1173,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G5">
         <v>300</v>
@@ -1189,7 +1202,7 @@
       </c>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1206,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G6">
         <v>300</v>
@@ -1222,7 +1235,7 @@
       </c>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1239,7 +1252,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G7">
         <v>300</v>
@@ -1255,7 +1268,7 @@
       </c>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1272,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -1288,7 +1301,7 @@
       </c>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -1305,7 +1318,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G9">
         <v>100</v>
@@ -1321,7 +1334,7 @@
       </c>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -1338,7 +1351,7 @@
         <v>28</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G10">
         <v>70</v>
@@ -1354,7 +1367,7 @@
       </c>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -1371,7 +1384,7 @@
         <v>28</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G11">
         <v>70</v>
@@ -1387,7 +1400,7 @@
       </c>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -1404,7 +1417,7 @@
         <v>28</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G12">
         <v>50</v>
@@ -1420,7 +1433,7 @@
       </c>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
@@ -1437,7 +1450,7 @@
         <v>8</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G13">
         <v>300</v>
@@ -1453,7 +1466,7 @@
       </c>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
@@ -1470,7 +1483,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G14">
         <v>300</v>
@@ -1486,7 +1499,7 @@
       </c>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
@@ -1503,7 +1516,7 @@
         <v>8</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G15">
         <v>150</v>
@@ -1519,7 +1532,7 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
@@ -1536,7 +1549,7 @@
         <v>44</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1552,7 +1565,7 @@
       </c>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>45</v>
       </c>
@@ -1569,7 +1582,7 @@
         <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1585,7 +1598,7 @@
       </c>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>47</v>
       </c>
@@ -1602,7 +1615,7 @@
         <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1618,7 +1631,7 @@
       </c>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
@@ -1635,7 +1648,7 @@
         <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1651,7 +1664,7 @@
       </c>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -1668,7 +1681,7 @@
         <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1684,7 +1697,7 @@
       </c>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>53</v>
       </c>
@@ -1701,7 +1714,7 @@
         <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1717,7 +1730,7 @@
       </c>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>55</v>
       </c>
@@ -1734,7 +1747,7 @@
         <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1750,7 +1763,7 @@
       </c>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -1767,7 +1780,7 @@
         <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1783,7 +1796,7 @@
       </c>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>59</v>
       </c>
@@ -1794,13 +1807,13 @@
         <v>36</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1816,7 +1829,7 @@
       </c>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>61</v>
       </c>
@@ -1833,7 +1846,7 @@
         <v>63</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1849,7 +1862,7 @@
       </c>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>64</v>
       </c>
@@ -1866,7 +1879,7 @@
         <v>44</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1882,7 +1895,7 @@
       </c>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>66</v>
       </c>
@@ -1899,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -1915,7 +1928,7 @@
       </c>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>69</v>
       </c>
@@ -1932,7 +1945,7 @@
         <v>44</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G28">
         <v>12</v>
@@ -1948,7 +1961,7 @@
       </c>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>73</v>
       </c>
@@ -1965,7 +1978,7 @@
         <v>44</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G29">
         <v>12</v>
@@ -1981,7 +1994,7 @@
       </c>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>75</v>
       </c>
@@ -1998,7 +2011,7 @@
         <v>44</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G30">
         <v>12</v>
@@ -2014,7 +2027,7 @@
       </c>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>77</v>
       </c>
@@ -2031,7 +2044,7 @@
         <v>44</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G31">
         <v>12</v>
@@ -2047,7 +2060,7 @@
       </c>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>79</v>
       </c>
@@ -2064,7 +2077,7 @@
         <v>44</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G32">
         <v>12</v>
@@ -2080,7 +2093,7 @@
       </c>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>81</v>
       </c>
@@ -2097,7 +2110,7 @@
         <v>44</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G33">
         <v>12</v>
@@ -2113,7 +2126,7 @@
       </c>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>83</v>
       </c>
@@ -2130,7 +2143,7 @@
         <v>44</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G34">
         <v>12</v>
@@ -2146,7 +2159,7 @@
       </c>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>85</v>
       </c>
@@ -2163,7 +2176,7 @@
         <v>44</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G35">
         <v>12</v>
@@ -2179,7 +2192,7 @@
       </c>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>87</v>
       </c>
@@ -2196,7 +2209,7 @@
         <v>8</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G36">
         <v>100</v>
@@ -2212,7 +2225,7 @@
       </c>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>89</v>
       </c>
@@ -2229,7 +2242,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G37">
         <v>300</v>
@@ -2245,7 +2258,7 @@
       </c>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>91</v>
       </c>
@@ -2262,7 +2275,7 @@
         <v>28</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G38">
         <v>50</v>
@@ -2278,7 +2291,7 @@
       </c>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>93</v>
       </c>
@@ -2295,7 +2308,7 @@
         <v>28</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G39">
         <v>50</v>
@@ -2311,7 +2324,7 @@
       </c>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>95</v>
       </c>
@@ -2328,7 +2341,7 @@
         <v>44</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2344,7 +2357,7 @@
       </c>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>97</v>
       </c>
@@ -2361,7 +2374,7 @@
         <v>28</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G41">
         <v>70</v>
@@ -2377,7 +2390,7 @@
       </c>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>99</v>
       </c>
@@ -2394,7 +2407,7 @@
         <v>8</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G42">
         <v>300</v>
@@ -2410,7 +2423,7 @@
       </c>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>101</v>
       </c>
@@ -2427,7 +2440,7 @@
         <v>44</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2443,7 +2456,7 @@
       </c>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
@@ -2460,7 +2473,7 @@
         <v>44</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2476,7 +2489,7 @@
       </c>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>106</v>
       </c>
@@ -2493,7 +2506,7 @@
         <v>28</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G45">
         <v>70</v>
@@ -2509,7 +2522,7 @@
       </c>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>108</v>
       </c>
@@ -2526,7 +2539,7 @@
         <v>8</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G46">
         <v>100</v>
@@ -2542,7 +2555,7 @@
       </c>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>110</v>
       </c>
@@ -2559,7 +2572,7 @@
         <v>28</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G47">
         <v>70</v>
@@ -2575,7 +2588,7 @@
       </c>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>112</v>
       </c>
@@ -2592,7 +2605,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G48">
         <v>300</v>
@@ -2608,7 +2621,7 @@
       </c>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>114</v>
       </c>
@@ -2625,7 +2638,7 @@
         <v>8</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G49">
         <v>100</v>
@@ -2641,7 +2654,7 @@
       </c>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>116</v>
       </c>
@@ -2658,7 +2671,7 @@
         <v>8</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G50">
         <v>300</v>
@@ -2674,7 +2687,7 @@
       </c>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>118</v>
       </c>
@@ -2691,7 +2704,7 @@
         <v>8</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G51">
         <v>300</v>
@@ -2707,7 +2720,7 @@
       </c>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>120</v>
       </c>
@@ -2724,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G52">
         <v>100</v>
@@ -2740,7 +2753,7 @@
       </c>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" ht="14.45" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>122</v>
       </c>
@@ -2757,7 +2770,7 @@
         <v>124</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2773,7 +2786,7 @@
       </c>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>125</v>
       </c>
@@ -2790,7 +2803,7 @@
         <v>44</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2806,7 +2819,7 @@
       </c>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>127</v>
       </c>
@@ -2823,7 +2836,7 @@
         <v>44</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2839,7 +2852,7 @@
       </c>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>129</v>
       </c>
@@ -2856,7 +2869,7 @@
         <v>44</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2872,7 +2885,7 @@
       </c>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>131</v>
       </c>
@@ -2889,7 +2902,7 @@
         <v>44</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2905,7 +2918,7 @@
       </c>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>133</v>
       </c>
@@ -2922,7 +2935,7 @@
         <v>44</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2938,7 +2951,7 @@
       </c>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>135</v>
       </c>
@@ -2955,7 +2968,7 @@
         <v>44</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2971,7 +2984,7 @@
       </c>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>137</v>
       </c>
@@ -2988,7 +3001,7 @@
         <v>44</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -3004,7 +3017,7 @@
       </c>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>139</v>
       </c>
@@ -3021,7 +3034,7 @@
         <v>44</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -3037,7 +3050,7 @@
       </c>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>141</v>
       </c>
@@ -3054,7 +3067,7 @@
         <v>44</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -3070,12 +3083,12 @@
       </c>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>143</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>71</v>
@@ -3087,7 +3100,7 @@
         <v>44</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -3103,7 +3116,7 @@
       </c>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>144</v>
       </c>
@@ -3120,7 +3133,7 @@
         <v>44</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G64">
         <v>500</v>
@@ -3136,7 +3149,7 @@
       </c>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>147</v>
       </c>
@@ -3153,7 +3166,7 @@
         <v>44</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -3169,7 +3182,7 @@
       </c>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -3186,7 +3199,7 @@
         <v>44</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -3202,7 +3215,7 @@
       </c>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>152</v>
       </c>
@@ -3219,7 +3232,7 @@
         <v>44</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -3235,7 +3248,7 @@
       </c>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>154</v>
       </c>
@@ -3252,7 +3265,7 @@
         <v>44</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -3268,7 +3281,7 @@
       </c>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>156</v>
       </c>
@@ -3285,7 +3298,7 @@
         <v>44</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3301,7 +3314,7 @@
       </c>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>158</v>
       </c>
@@ -3318,7 +3331,7 @@
         <v>44</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3334,7 +3347,7 @@
       </c>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>160</v>
       </c>
@@ -3351,7 +3364,7 @@
         <v>44</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3367,7 +3380,7 @@
       </c>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>162</v>
       </c>
@@ -3384,7 +3397,7 @@
         <v>44</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3400,7 +3413,7 @@
       </c>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>164</v>
       </c>
@@ -3417,7 +3430,7 @@
         <v>44</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3433,7 +3446,7 @@
       </c>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>166</v>
       </c>
@@ -3450,7 +3463,7 @@
         <v>44</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3466,7 +3479,7 @@
       </c>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>168</v>
       </c>
@@ -3483,7 +3496,7 @@
         <v>44</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G75">
         <v>12</v>
@@ -3499,7 +3512,7 @@
       </c>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>170</v>
       </c>
@@ -3516,7 +3529,7 @@
         <v>44</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G76">
         <v>12</v>
@@ -3532,45 +3545,45 @@
       </c>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" s="2">
+        <v>920</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2">
+        <v>1</v>
+      </c>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G77">
-        <v>300</v>
-      </c>
-      <c r="H77" s="2">
-        <v>16</v>
-      </c>
-      <c r="I77" s="2">
-        <v>0</v>
-      </c>
-      <c r="J77" s="2">
-        <v>1</v>
-      </c>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A78" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>6</v>
@@ -3582,13 +3595,13 @@
         <v>44</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G78">
         <v>300</v>
       </c>
       <c r="H78" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I78" s="2">
         <v>0</v>
@@ -3598,30 +3611,30 @@
       </c>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G79">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="H79" s="2">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I79" s="2">
         <v>0</v>
@@ -3631,30 +3644,30 @@
       </c>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G80">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="H80" s="2">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="I80" s="2">
         <v>0</v>
@@ -3664,27 +3677,27 @@
       </c>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G81">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H81" s="2">
         <v>19</v>
@@ -3697,91 +3710,166 @@
       </c>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G82">
+        <v>100</v>
+      </c>
+      <c r="H82" s="2">
+        <v>19</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2">
+        <v>1</v>
+      </c>
+      <c r="K82" s="2"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="E83" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F83" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G83">
+        <v>70</v>
+      </c>
+      <c r="H83" s="2">
+        <v>36</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2">
+        <v>1</v>
+      </c>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G82">
+      <c r="E84" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G84">
         <v>70</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H84" s="2">
         <v>36</v>
       </c>
-      <c r="I82" s="2">
-        <v>0</v>
-      </c>
-      <c r="J82" s="2">
-        <v>1</v>
-      </c>
-      <c r="K82" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
+      <c r="J84" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>190</v>
+      <c r="D85" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G85">
+        <v>300</v>
+      </c>
+      <c r="H85" s="2">
+        <v>16</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G86">
+        <v>100</v>
+      </c>
+      <c r="H86" s="2">
+        <v>19</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
